--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487686_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487686_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. HERMOSO ALCUBILLA</t>
+          <t>N. LASUNCION MARIBLANCA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9341</v>
+        <v>2.5776</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8985</v>
+        <v>3.8347</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0356</v>
+        <v>-1.2571</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.6601</v>
+        <v>1.9504</v>
       </c>
       <c r="H2" t="n">
-        <v>-3.1842</v>
+        <v>-2.5853</v>
       </c>
       <c r="I2" t="n">
-        <v>2.5242</v>
+        <v>4.5357</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.2462</v>
+        <v>3.9275</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.5859</v>
+        <v>-0.5026</v>
       </c>
       <c r="L2" t="n">
-        <v>1.3397</v>
+        <v>4.4301</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.4138</v>
+        <v>-1.9771</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.5983</v>
+        <v>-2.0828</v>
       </c>
       <c r="O2" t="n">
-        <v>1.1845</v>
+        <v>0.1056</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.9403</v>
+        <v>0.5821</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.1045</v>
+        <v>-0.194</v>
       </c>
       <c r="R2" t="n">
-        <v>1.1642</v>
+        <v>0.7761</v>
       </c>
       <c r="S2" t="n">
-        <v>3.6987</v>
+        <v>0.0451</v>
       </c>
       <c r="T2" t="n">
-        <v>2.7433</v>
+        <v>0.1012</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9554</v>
+        <v>-0.0561</v>
       </c>
       <c r="V2" t="n">
-        <v>1.8358</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.506</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0.3299</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2264</v>
+        <v>2.0356</v>
       </c>
       <c r="E3" t="n">
         <v>1.2997</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9266</v>
+        <v>0.7359</v>
       </c>
       <c r="G3" t="n">
         <v>1.1488</v>
@@ -688,13 +688,13 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6119</v>
+        <v>0.4212</v>
       </c>
       <c r="T3" t="n">
         <v>0.1335</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4785</v>
+        <v>0.2877</v>
       </c>
       <c r="V3" t="n">
         <v>0.6597</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1692</v>
+        <v>1.881</v>
       </c>
       <c r="E4" t="n">
-        <v>2.747</v>
+        <v>2.5678</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.5778</v>
+        <v>-0.6869</v>
       </c>
       <c r="G4" t="n">
         <v>3.5207</v>
@@ -766,13 +766,13 @@
         <v>0.7761</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8605</v>
+        <v>0.5723</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6931</v>
+        <v>0.5139</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1674</v>
+        <v>0.0584</v>
       </c>
       <c r="V4" t="n">
         <v>-0.6597</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6937</v>
+        <v>1.742</v>
       </c>
       <c r="E5" t="n">
-        <v>4.5065</v>
+        <v>4.5275</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.8128</v>
+        <v>-2.7856</v>
       </c>
       <c r="G5" t="n">
         <v>1.2316</v>
@@ -844,13 +844,13 @@
         <v>1.5523</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5397</v>
+        <v>0.588</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3903</v>
+        <v>0.4113</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1494</v>
+        <v>0.1767</v>
       </c>
       <c r="V5" t="n">
         <v>-0.6597</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. LASUNCION MARIBLANCA</t>
+          <t>M. KREISLER LORENTE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6835</v>
+        <v>0.8561</v>
       </c>
       <c r="E6" t="n">
-        <v>3.2131</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.5296</v>
+        <v>-0.0799</v>
       </c>
       <c r="G6" t="n">
-        <v>1.9504</v>
+        <v>1.1443</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.5853</v>
+        <v>0.3897</v>
       </c>
       <c r="I6" t="n">
-        <v>4.5357</v>
+        <v>0.7546</v>
       </c>
       <c r="J6" t="n">
-        <v>3.9275</v>
+        <v>1.863</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5026</v>
+        <v>1.0916</v>
       </c>
       <c r="L6" t="n">
-        <v>4.4301</v>
+        <v>0.7713</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.9771</v>
+        <v>-0.7187</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.0828</v>
+        <v>-0.7019</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1056</v>
+        <v>-0.0167</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5821</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.194</v>
+        <v>-1.3582</v>
       </c>
       <c r="R6" t="n">
         <v>0.7761</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.849</v>
+        <v>0.5759</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5204</v>
+        <v>0.4312</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3286</v>
+        <v>0.1447</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. KREISLER LORENTE</t>
+          <t>M. HERMOSO ALCUBILLA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0716</v>
+        <v>0.6963</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3354</v>
+        <v>-0.9033</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.407</v>
+        <v>1.5995</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1443</v>
+        <v>-0.6601</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3897</v>
+        <v>-3.1842</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7546</v>
+        <v>2.5242</v>
       </c>
       <c r="J7" t="n">
-        <v>1.863</v>
+        <v>-0.2462</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0916</v>
+        <v>-1.5859</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7713</v>
+        <v>1.3397</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7187</v>
+        <v>-0.4138</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7019</v>
+        <v>-1.5983</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0167</v>
+        <v>1.1845</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.5821</v>
+        <v>-1.9403</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.3582</v>
+        <v>-3.1045</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7761</v>
+        <v>1.1642</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3517</v>
+        <v>1.4609</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1694</v>
+        <v>0.9415</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1824</v>
+        <v>0.5193</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2821</v>
+        <v>1.8358</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.506</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2821</v>
+        <v>0.3299</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4125</v>
+        <v>0.3454</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8812</v>
+        <v>1.5028</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2938</v>
+        <v>-1.1575</v>
       </c>
       <c r="G8" t="n">
         <v>1.1245</v>
@@ -1078,13 +1078,13 @@
         <v>0.5821</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8310999999999999</v>
+        <v>-0.0732</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5204</v>
+        <v>0.1012</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3107</v>
+        <v>-0.1744</v>
       </c>
       <c r="V8" t="n">
         <v>0.8462</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. MARTINEZ SANTOS</t>
+          <t>P. FUENTE DIEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7183</v>
+        <v>-1.1298</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5083</v>
+        <v>-2.8288</v>
       </c>
       <c r="F9" t="n">
-        <v>0.79</v>
+        <v>1.699</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8699</v>
+        <v>1.5251</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.2531</v>
+        <v>0.3996</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3832</v>
+        <v>1.1256</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.4971</v>
+        <v>0.8255</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.9516</v>
+        <v>0.7621</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5455</v>
+        <v>0.0634</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6271</v>
+        <v>0.6996</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3015</v>
+        <v>-0.3625</v>
       </c>
       <c r="O9" t="n">
-        <v>0.9287</v>
+        <v>1.0622</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5821</v>
+        <v>-2.1344</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.194</v>
+        <v>-3.1045</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7761</v>
+        <v>0.9702</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7934</v>
+        <v>0.1391</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1828</v>
+        <v>0.1099</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6106</v>
+        <v>0.0292</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2239</v>
+        <v>-0.6597</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.6597</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. FUENTE DIEZ</t>
+          <t>J. GARCIA-LARRACHE SEGURA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.5847</v>
+        <v>-1.1361</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.2292</v>
+        <v>-2.7219</v>
       </c>
       <c r="F10" t="n">
-        <v>1.6445</v>
+        <v>1.5858</v>
       </c>
       <c r="G10" t="n">
-        <v>1.5251</v>
+        <v>-1.2069</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3996</v>
+        <v>-1.1724</v>
       </c>
       <c r="I10" t="n">
-        <v>1.1256</v>
+        <v>-0.0345</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8255</v>
+        <v>-1.2165</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7621</v>
+        <v>-0.5314</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0634</v>
+        <v>-0.6851</v>
       </c>
       <c r="M10" t="n">
-        <v>0.6996</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3625</v>
+        <v>-0.641</v>
       </c>
       <c r="O10" t="n">
-        <v>1.0622</v>
+        <v>0.6506</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.1344</v>
+        <v>-1.1642</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.1045</v>
+        <v>-1.9403</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9702</v>
+        <v>0.7761</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3158</v>
+        <v>0.5274</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2905</v>
+        <v>0.4349</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0253</v>
+        <v>0.0926</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6597</v>
+        <v>0.7075</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.6597</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>0.7075</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>L. GARCIA LARRACHE SEGURA</t>
+          <t>J. MARTINEZ SANTOS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.5935</v>
+        <v>-1.2728</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.2535</v>
+        <v>-1.7085</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.34</v>
+        <v>0.4357</v>
       </c>
       <c r="G11" t="n">
-        <v>1.4321</v>
+        <v>-0.8699</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3197</v>
+        <v>-1.2531</v>
       </c>
       <c r="I11" t="n">
-        <v>1.7518</v>
+        <v>0.3832</v>
       </c>
       <c r="J11" t="n">
-        <v>2.0463</v>
+        <v>-1.4971</v>
       </c>
       <c r="K11" t="n">
-        <v>1.3512</v>
+        <v>-0.9516</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6952</v>
+        <v>-0.5455</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6142</v>
+        <v>0.6271</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.6708</v>
+        <v>-0.3015</v>
       </c>
       <c r="O11" t="n">
-        <v>1.0566</v>
+        <v>0.9287</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.3284</v>
+        <v>0.5821</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.9105</v>
+        <v>-0.194</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5821</v>
+        <v>0.7761</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4789</v>
+        <v>0.2389</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3286</v>
+        <v>-0.0174</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1503</v>
+        <v>0.2563</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.1761</v>
+        <v>-1.2239</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.4582</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. GARCIA-LARRACHE SEGURA</t>
+          <t>L. GARCIA LARRACHE SEGURA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.6333</v>
+        <v>-1.2965</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.0828</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>1.4495</v>
+        <v>-1.2037</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.2069</v>
+        <v>1.4321</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.1724</v>
+        <v>-0.3197</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.0345</v>
+        <v>1.7518</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.2165</v>
+        <v>2.0463</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.5314</v>
+        <v>1.3512</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6851</v>
+        <v>0.6952</v>
       </c>
       <c r="M12" t="n">
-        <v>0.009599999999999999</v>
+        <v>-0.6142</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.641</v>
+        <v>-1.6708</v>
       </c>
       <c r="O12" t="n">
-        <v>0.6506</v>
+        <v>1.0566</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.1642</v>
+        <v>-2.3284</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9403</v>
+        <v>-2.9105</v>
       </c>
       <c r="R12" t="n">
-        <v>0.7761</v>
+        <v>0.5821</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0303</v>
+        <v>0.7759</v>
       </c>
       <c r="T12" t="n">
-        <v>0.074</v>
+        <v>0.4893</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0437</v>
+        <v>0.2866</v>
       </c>
       <c r="V12" t="n">
-        <v>0.7075</v>
+        <v>-1.1761</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X12" t="n">
-        <v>0.7075</v>
+        <v>-1.4582</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.692999999999999</v>
+        <v>5.298800000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>5.807599999999997</v>
+        <v>6.413200000000002</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.1148</v>
+        <v>-1.114800000000001</v>
       </c>
       <c r="G13" t="n">
         <v>10.3406</v>
@@ -1456,31 +1456,31 @@
         <v>-12.2839</v>
       </c>
       <c r="O13" t="n">
-        <v>5.1437</v>
+        <v>5.143700000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>-9.701699999999999</v>
+        <v>-9.701700000000001</v>
       </c>
       <c r="Q13" t="n">
         <v>-18.433</v>
       </c>
       <c r="R13" t="n">
-        <v>8.731400000000001</v>
+        <v>8.731399999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>4.665800000000001</v>
+        <v>5.2715</v>
       </c>
       <c r="T13" t="n">
-        <v>3.0449</v>
+        <v>3.6505</v>
       </c>
       <c r="U13" t="n">
-        <v>1.6209</v>
+        <v>1.621</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.6120000000000001</v>
+        <v>-0.6119999999999997</v>
       </c>
       <c r="W13" t="n">
-        <v>3.714899999999999</v>
+        <v>3.7149</v>
       </c>
       <c r="X13" t="n">
         <v>-4.3268</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.041</v>
+        <v>2.9883</v>
       </c>
       <c r="E14" t="n">
-        <v>4.5737</v>
+        <v>2.7719</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4673</v>
+        <v>0.2164</v>
       </c>
       <c r="G14" t="n">
         <v>0.214</v>
@@ -1546,13 +1546,13 @@
         <v>2.9105</v>
       </c>
       <c r="S14" t="n">
-        <v>2.2748</v>
+        <v>0.2221</v>
       </c>
       <c r="T14" t="n">
-        <v>1.9806</v>
+        <v>0.1788</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2941</v>
+        <v>0.0432</v>
       </c>
       <c r="V14" t="n">
         <v>0.6119</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5053</v>
+        <v>2.3366</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4255</v>
+        <v>3.1262</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9203</v>
+        <v>-0.7896</v>
       </c>
       <c r="G15" t="n">
         <v>0.9856</v>
@@ -1624,13 +1624,13 @@
         <v>2.5224</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.2191</v>
+        <v>-0.3878</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9926</v>
+        <v>-0.2919</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2265</v>
+        <v>-0.0959</v>
       </c>
       <c r="V15" t="n">
         <v>0.1865</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.264</v>
+        <v>1.0225</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0551</v>
+        <v>0.6556999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2089</v>
+        <v>0.3669</v>
       </c>
       <c r="G16" t="n">
         <v>-0.7712</v>
@@ -1702,13 +1702,13 @@
         <v>2.1344</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9946</v>
+        <v>-0.2361</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8233</v>
+        <v>-0.2227</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1713</v>
+        <v>-0.0134</v>
       </c>
       <c r="V16" t="n">
         <v>1.8358</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1944</v>
+        <v>0.7066</v>
       </c>
       <c r="E17" t="n">
         <v>1.0292</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8348</v>
+        <v>-0.3225</v>
       </c>
       <c r="G17" t="n">
         <v>-0.0308</v>
@@ -1780,13 +1780,13 @@
         <v>1.3582</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.133</v>
+        <v>-0.6208</v>
       </c>
       <c r="T17" t="n">
         <v>-0.2894</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8436</v>
+        <v>-0.3314</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. SANTANA OJEDA</t>
+          <t>P. SÁNCHEZ GUTIERREZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1245</v>
+        <v>0.5185</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.2965</v>
+        <v>2.2851</v>
       </c>
       <c r="F18" t="n">
-        <v>1.172</v>
+        <v>-1.7666</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.1003</v>
+        <v>-0.1489</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0849</v>
+        <v>2.6529</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.0155</v>
+        <v>-2.8017</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5092</v>
+        <v>2.7562</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7621</v>
+        <v>3.3779</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.2712</v>
+        <v>-0.6217</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5911999999999999</v>
+        <v>-2.905</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8469</v>
+        <v>-0.725</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2558</v>
+        <v>-2.18</v>
       </c>
       <c r="P18" t="n">
-        <v>1.7463</v>
+        <v>1.9403</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7463</v>
+        <v>1.9403</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7705</v>
+        <v>-0.7088</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7874</v>
+        <v>-0.4711</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0168</v>
+        <v>-0.2378</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.5642</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.5642</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. SÁNCHEZ GUTIERREZ</t>
+          <t>A. SANTANA OJEDA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3124</v>
+        <v>0.4732</v>
       </c>
       <c r="E19" t="n">
-        <v>1.8847</v>
+        <v>-0.6959</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.1971</v>
+        <v>1.1692</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1489</v>
+        <v>-1.1003</v>
       </c>
       <c r="H19" t="n">
-        <v>2.6529</v>
+        <v>-0.0849</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.8017</v>
+        <v>-1.0155</v>
       </c>
       <c r="J19" t="n">
-        <v>2.7562</v>
+        <v>-0.5092</v>
       </c>
       <c r="K19" t="n">
-        <v>3.3779</v>
+        <v>0.7621</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6217</v>
+        <v>-1.2712</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.905</v>
+        <v>-0.5911999999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.725</v>
+        <v>-0.8469</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.18</v>
+        <v>0.2558</v>
       </c>
       <c r="P19" t="n">
-        <v>1.9403</v>
+        <v>1.7463</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.9403</v>
+        <v>1.7463</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.5397</v>
+        <v>-0.1727</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8715000000000001</v>
+        <v>-0.1868</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6682</v>
+        <v>0.014</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.5642</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5642</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.511</v>
+        <v>-0.6933</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.6593</v>
+        <v>-3.0597</v>
       </c>
       <c r="F20" t="n">
-        <v>2.1484</v>
+        <v>2.3664</v>
       </c>
       <c r="G20" t="n">
         <v>-1.3602</v>
@@ -2014,13 +2014,13 @@
         <v>2.7164</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0253</v>
+        <v>-0.157</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3779</v>
+        <v>-0.0225</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3526</v>
+        <v>-0.1346</v>
       </c>
       <c r="V20" t="n">
         <v>0.0478</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. VIDAL RODRIGUEZ</t>
+          <t>E. VIDAL RODRIGUEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8657</v>
+        <v>-1.9458</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9093</v>
+        <v>-0.7104</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9564</v>
+        <v>-1.2354</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.6059</v>
+        <v>-1.9674</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.1015</v>
+        <v>-0.3897</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5044</v>
+        <v>-1.5777</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5649</v>
+        <v>-0.326</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6055</v>
+        <v>0.3007</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0406</v>
+        <v>-0.6267</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.041</v>
+        <v>-1.6414</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.496</v>
+        <v>-0.6904</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.545</v>
+        <v>-0.951</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.3582</v>
+        <v>0.5821</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9403</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0.5821</v>
       </c>
       <c r="S21" t="n">
-        <v>1.1462</v>
+        <v>-0.5605</v>
       </c>
       <c r="T21" t="n">
-        <v>1.0318</v>
+        <v>-0.3844</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1144</v>
+        <v>-0.1761</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.0478</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5642</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.6119</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E. VIDAL RODRIGUEZ</t>
+          <t>A. VIDAL RODRIGUEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.2339</v>
+        <v>-2.5692</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.8105</v>
+        <v>-1.61</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4233</v>
+        <v>-0.9592000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.9674</v>
+        <v>-1.6059</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.3897</v>
+        <v>-1.1015</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.5777</v>
+        <v>-0.5044</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.326</v>
+        <v>-0.5649</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3007</v>
+        <v>-0.6055</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6267</v>
+        <v>0.0406</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.6414</v>
+        <v>-1.041</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6904</v>
+        <v>-0.496</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.951</v>
+        <v>-0.545</v>
       </c>
       <c r="P22" t="n">
-        <v>0.5821</v>
+        <v>-1.3582</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.9403</v>
       </c>
       <c r="R22" t="n">
         <v>0.5821</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8486</v>
+        <v>0.4427</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4845</v>
+        <v>0.3311</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3641</v>
+        <v>0.1116</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.0478</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.5642</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.6119</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. JIMENEZ HERNANDEZ</t>
+          <t>G. ARTILES ROMERO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.2905</v>
+        <v>-2.7078</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.4699</v>
+        <v>-1.4076</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.8206</v>
+        <v>-1.3002</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.0557</v>
+        <v>-2.4998</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.1509</v>
+        <v>0.5165999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.9048</v>
+        <v>-3.0164</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.2698</v>
+        <v>-1.1752</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.8609</v>
+        <v>0.7456</v>
       </c>
       <c r="L23" t="n">
-        <v>0.5911999999999999</v>
+        <v>-1.9208</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.786</v>
+        <v>-1.3246</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.29</v>
+        <v>-0.229</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.496</v>
+        <v>-1.0956</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.3881</v>
+        <v>1.3582</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.5821</v>
+        <v>1.3582</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6124000000000001</v>
+        <v>-0.3424</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2299</v>
+        <v>-0.2325</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3824</v>
+        <v>-0.1099</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.2343</v>
+        <v>-1.2239</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.2343</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>G. ARTILES ROMERO</t>
+          <t>J. JIMENEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.3596</v>
+        <v>-2.8206</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.7079</v>
+        <v>-1.2697</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.6517</v>
+        <v>-1.5509</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.4998</v>
+        <v>-2.0557</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5165999999999999</v>
+        <v>-1.1509</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.0164</v>
+        <v>-0.9048</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.1752</v>
+        <v>-0.2698</v>
       </c>
       <c r="K24" t="n">
-        <v>0.7456</v>
+        <v>-0.8609</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.9208</v>
+        <v>0.5911999999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.3246</v>
+        <v>-1.786</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.229</v>
+        <v>-0.29</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.0956</v>
+        <v>-1.496</v>
       </c>
       <c r="P24" t="n">
-        <v>1.3582</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3582</v>
+        <v>0.5821</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9942</v>
+        <v>-0.1424</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5328000000000001</v>
+        <v>-0.0297</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4614</v>
+        <v>-0.1127</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.2239</v>
+        <v>-0.2343</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.2239</v>
+        <v>-0.2343</v>
       </c>
     </row>
     <row r="25">
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.6929</v>
+        <v>-2.691000000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>1.114800000000001</v>
+        <v>1.114799999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.8076</v>
+        <v>-3.8055</v>
       </c>
       <c r="G25" t="n">
         <v>-10.3406</v>
       </c>
       <c r="H25" t="n">
-        <v>4.424299999999999</v>
+        <v>4.424300000000001</v>
       </c>
       <c r="I25" t="n">
         <v>-14.7649</v>
@@ -2383,7 +2383,7 @@
         <v>12.2841</v>
       </c>
       <c r="L25" t="n">
-        <v>-5.1437</v>
+        <v>-5.143700000000001</v>
       </c>
       <c r="M25" t="n">
         <v>-17.4811</v>
@@ -2392,25 +2392,25 @@
         <v>-7.8598</v>
       </c>
       <c r="O25" t="n">
-        <v>-9.621099999999998</v>
+        <v>-9.6211</v>
       </c>
       <c r="P25" t="n">
         <v>9.701500000000001</v>
       </c>
       <c r="Q25" t="n">
-        <v>-8.7315</v>
+        <v>-8.731499999999999</v>
       </c>
       <c r="R25" t="n">
         <v>18.433</v>
       </c>
       <c r="S25" t="n">
-        <v>-4.665800000000001</v>
+        <v>-2.6637</v>
       </c>
       <c r="T25" t="n">
         <v>-1.6211</v>
       </c>
       <c r="U25" t="n">
-        <v>-3.0448</v>
+        <v>-1.043</v>
       </c>
       <c r="V25" t="n">
         <v>0.6117999999999999</v>
@@ -2419,7 +2419,7 @@
         <v>4.3268</v>
       </c>
       <c r="X25" t="n">
-        <v>-3.714900000000001</v>
+        <v>-3.7149</v>
       </c>
     </row>
   </sheetData>
